--- a/Planilha_Producao_Brumas.xlsx
+++ b/Planilha_Producao_Brumas.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,34 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -88,8 +114,14 @@
         <bgColor rgb="00D4A017"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+        <bgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -103,11 +135,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -126,6 +186,71 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -492,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -503,15 +628,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PLANILHA DE PRODUÇÃO – JOGO SÉRIO BRUMAS (Build 1 – Entrega 19/04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>PLANILHA DE PRODUÇÃO – JOGO SÉRIO BRUMAS</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>LEGENDA DE STATUS (aplicar cor na célula):</t>
         </is>
@@ -534,556 +658,505 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>INFORMAÇÕES IMPORTANTES DO PROJETO (preencher e manter atualizado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Paleta de Cores (sugestão)</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Amarelo Sol (#F2C94C), Amarelo Escuro (#D4A017), Marrom Terra (#8B6914), Verde Musgo (#556B2F), Cinza (#808080) — DEFINIR COM A EQUIPE antes de aplicar em qualquer asset ou interface</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n"/>
+      <c r="D7" s="20" t="n"/>
+      <c r="E7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Link do GDR</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>(inserir link aqui)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="21" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Pasta Pinterest / Moodboard</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>(inserir link aqui)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="21" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Repositório GitHub</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>https://github.com/AndreHP950/Brumas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Roteiro do Benício</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>(inserir link ou localização — o roteiro já existe em formato texto, foco é transformar em jogo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Build mais recente (APK)</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>(inserir link ou localização aqui)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Referências visuais</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>(inserir links ou pastas aqui)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Observações</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Máx 1-3 tarefas/pessoa/semana. Respeitar dependências. A história do Benício já está pronta. Foco da Build 1: funcional, não visual.</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>CRONOGRAMA DE ENTREGAS</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Pontos</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Build Inicial</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>19/04</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>15 pts</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Build Intermediária</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>17/05</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>15 pts</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Build Pré-banca</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14/06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Build Final para Banca</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>28/06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>50 pts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>LINHA DE EXEMPLO (COMO PREENCHER)</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="21" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>André Henriques</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>Antonio Araujo</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D23" s="27" t="inlineStr">
         <is>
           <t>Arthur Doffémond</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Laura Alairce</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>EXEMPLO
 (Tarefa)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Criar o menu principal do jogo com todas as opções de navegação funcionais (Iniciar, Configurações, Sair). O menu deve seguir a paleta de cores definida (amarelo #F2C94C como destaque, fundo escuro para contraste). Os botões devem ter feedback visual ao clicar.</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Atualizar o GDR com a seção de identidade visual completa, incluindo referências de jogos sérios similares, definição da paleta de cores oficial e direção de arte.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Criar o sistema de navegação completo entre as telas do jogo (menu → seleção → jogo → etc). O sistema deve permitir ir para qualquer tela e voltar para a anterior.</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Escrever o roteiro completo do personagem Benício com todos os trechos narrativos e as ramificações de escolha. Mapear os caminhos possíveis em um fluxograma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Criar o projeto do jogo na Unity e organizar todas as pastas necessárias (Scripts, Cenas, UI, Modelos, Áudio). Configurar o projeto para build Android. Criar as cenas iniciais vazias (Menu, Jogo).</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Criar moodboard no Pinterest junto com a Laura, focado em cenários e ambientação. Pesquisar referências de: cenários low poly de cidades pequenas, mineração, natureza brasileira, referências visuais de Brumadinho. Documentar a direção de arte de cenários no GDR.</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Pesquisar e estudar como implementar sistema de narrativa e escolhas na Unity. Documentar as opções encontradas (ex: Ink, Yarn Spinner, sistema próprio com strings) com prós e contras. Compartilhar com a equipe para decisão.</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Criar esboços/wireframes da interface de narrativa: onde fica o texto, onde ficam os botões de escolha, layout dos botões do menu e de controle (avançar, voltar). Compartilhar com a equipe para aprovação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>EXEMPLO
 (O que fiz + Commit)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Criei o menu principal usando Canvas no Unity. Implementei 3 botões (Iniciar, Configurações, Sair) com a paleta de cores definida. O botão Iniciar leva para a tela de seleção de personagem. Configurações abre um painel com controle de volume. Sair fecha o jogo. Adicionei animação de hover nos botões. Falta: ajustar para diferentes resoluções de celular.
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Criei o projeto Unity, organizei as pastas. Configurei para Android. Criei 2 cenas vazias: MainMenu e GameScene.
 Commit: [INSERIR LINK]</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Pesquisei 10 jogos sérios de referência (That Dragon Cancer, Valiant Hearts, Papers Please, etc). Documentei no GDR o que funciona em cada um e o que podemos aproveitar. Defini a paleta oficial: Amarelo (#F2C94C), Amarelo Escuro (#D4A017), Marrom (#8B6914), Verde Musgo (#556B2F), Cinza (#808080). Criei guia de quando usar cada cor.
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Pesquisei referências de cenários low poly e cidades brasileiras. Montei moodboard no Pinterest com 20+ imagens. Documentei direção de arte no GDR.
 Commit: [INSERIR LINK]</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Criei o sistema de navegação entre cenas usando o SceneManager do Unity. Funciona com fade de transição entre telas. Testei navegação entre menu e cena de jogo, funcionando sem erros. Falta: integrar com sistema de narrativa.
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Pesquisei 3 opções: Ink, Yarn Spinner e sistema próprio. Documentei prós e contras. Recomendo sistema próprio com strings por ser mais simples.
 Commit: [INSERIR LINK]</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Escrevi o roteiro completo do Benício com 12 trechos narrativos. Cada trecho tem texto + opções de escolha que levam a diferentes caminhos. Criei fluxograma no Figma mostrando todas as ramificações. Exportei o roteiro em JSON para facilitar integração com Unity. Falta: revisão ortográfica.
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Criei wireframes da tela de narrativa e botões de escolha. Fiz 3 versões de layout. A equipe aprovou a versão 2.
 Commit: [INSERIR LINK]</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>SEMANA 1: 05/04 – 11/04 (Estrutura Base + Planejamento)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>SEMANA 1: 05/04 – 11/04 (Planejamento + Estrutura Base)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>⚠️ Foco: Definir paleta, referências visuais, estrutura do projeto e planejar a interface ANTES de implementar. A história do Benício já existe — não precisa reescrever.</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="21" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>André Henriques</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>Antonio Araujo</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Arthur Doffémond</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>Laura Alairce</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>05/04 – 11/04
-(Tarefa 1)</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Criar o projeto do jogo na Unity e organizar todas as pastas necessárias (scripts, cenas, áudio, modelos, UI, etc). Configurar o projeto para build Android. Criar as cenas iniciais vazias que vamos precisar (menu, jogo, seleção).</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Atualizar o GDR com referências visuais e narrativas de jogos sérios similares ao nosso. Pesquisar pelo menos 10 jogos de referência, documentar o que funciona em cada um e o que podemos aproveitar no Brumas.</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Criar o sistema básico de navegação entre as telas do jogo. O jogador precisa conseguir ir de uma tela para outra (ex: menu → jogo) e voltar. Implementar transição simples entre as telas.</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Escrever o roteiro completo do personagem Benício com todos os trechos narrativos. Definir todas as opções de escolha e para onde cada uma leva. Criar um fluxograma mostrando todos os caminhos possíveis da história.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+(Tarefa)</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Criar o projeto do jogo na Unity e organizar a estrutura de pastas (Scripts, Cenas, UI, Modelos, Áudio). Configurar o projeto para build Android. Criar as cenas iniciais vazias que vamos precisar (Menu, Jogo). Configurar o .gitignore adequado para Unity.</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Criar moodboard no Pinterest junto com a Laura, focado em cenários e ambientação. Pesquisar referências de: cenários low poly de cidades pequenas, mineração, natureza brasileira, referências visuais de Brumadinho. Documentar a direção de arte de cenários no GDR.</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>Pesquisar e estudar como implementar sistema de narrativa e escolhas na Unity. Documentar as opções encontradas (ex: Ink, Yarn Spinner, sistema próprio com strings) com prós e contras de cada uma. Compartilhar com a equipe para decisão conjunta.</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>Criar moodboard no Pinterest junto com o Antonio, focado em cenários e ambientação. Pesquisar referências de interface de jogos narrativos para celular (layout de texto, botões de escolha, tipografia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>05/04 – 11/04
-(O que fiz + Commit 1)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr"/>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+(O que fiz + Commit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>05/04 – 11/04
-(Tarefa 2)</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Implementar o menu principal funcional do jogo com os botões: Iniciar, Configurações e Sair. Seguir a paleta de cores definida (amarelo #F2C94C como cor primária de destaque, fundo com bom contraste). Os botões devem ter feedback visual ao interagir. Fonte legível e adequada para todas as idades.</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Definir a paleta de cores oficial do projeto e documentar no GDR. A paleta deve ter foco em tons de amarelo. Definir quando cada cor deve ser usada (botões, fundos, textos, etc). Cores definidas: Amarelo Sol (#F2C94C), Amarelo Escuro (#D4A017), Marrom Terra (#8B6914), Verde Musgo (#556B2F), Cinza (#808080).</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Criar o sistema básico de escolhas do jogo. O jogador precisa ver opções de escolha na tela e poder selecionar uma, que leva a um novo trecho da história. Testar com algumas escolhas de exemplo para garantir que funciona.</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>Criar moodboard no Pinterest com a identidade visual do jogo. Incluir referências de: cenários low poly, interfaces simples e minimalistas, paletas de cores quentes/amarelo, jogos narrativos. Compartilhar com a equipe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>05/04 – 11/04
-(O que fiz + Commit 2)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr"/>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>05/04 – 11/04
-(Tarefa 3)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>Implementar a tela de seleção de personagem. Inicialmente só teremos o Benício, mas a tela deve permitir selecionar o personagem e iniciar a história dele. Preparar a estrutura para no futuro adicionar outros personagens.</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Criar moodboard no Pinterest junto com a Laura, focado em cenários e ambientação. Pesquisar referências de: cenários low poly de cidades pequenas, mineração, natureza brasileira, referências visuais de Brumadinho. Documentar a direção de arte de cenários no GDR.</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Criar o sistema de histórico de decisões do jogador. O jogo deve guardar quais escolhas o jogador fez ao longo da história, para poder consultar depois. Criar uma tela simples onde o jogador pode ver o histórico das suas decisões.</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>Criar os conceitos visuais 2D para a interface do jogo: sprites de botões (seguindo a paleta de cores), painéis de diálogo/narrativa, e ícones para o menu e navegação. Os assets devem funcionar bem em tela de celular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>05/04 – 11/04
-(O que fiz + Commit 3)</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr"/>
-      <c r="D18" s="10" t="inlineStr"/>
-      <c r="E18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>SEMANA 2: 12/04 – 18/04 (FOCO TOTAL – Integração e Build)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>André Henriques</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Antonio Araujo</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Arthur Doffémond</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Laura Alairce</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(Tarefa 1)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>Implementar o sistema de narrativa completo. O jogo deve conseguir carregar a história, exibir os trechos de texto, e permitir o jogador avançar, voltar e reler o trecho atual. Integrar com a interface de narrativa (painel de texto e botões de navegação).</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Modelar o cenário base no Blender em estilo low poly para a blocagem. Criar os elementos principais: terreno, casas simples, vegetação básica, e área da barragem. Usar formas simples e cores sólidas da paleta. Exportar para Unity.</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Integrar o sistema de escolhas com o sistema de narrativa. Quando o jogador faz uma escolha, o jogo deve registrar a decisão e avançar para o trecho correto. Testar o fluxo completo da história do início ao fim, passando por pelo menos 2 caminhos diferentes.</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Converter o roteiro final para um formato que o jogo consiga ler (JSON, planilha ou outro formato que a equipe decidir). Garantir que todos os caminhos da história estão corretos e não tem becos sem saída. Testar a importação no Unity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(O que fiz + Commit 1)</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr"/>
-      <c r="C23" s="10" t="inlineStr"/>
-      <c r="D23" s="10" t="inlineStr"/>
-      <c r="E23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(Tarefa 2)</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>Implementar o sistema de áudio básico do jogo. O jogo deve ter: música de fundo, efeitos sonoros nos botões, e suporte para narração nos trechos da história. Criar controle de volume nas configurações.</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Aplicar as cores e materiais da paleta nos modelos do cenário. Ajustar a iluminação da cena para ficar agradável. Configurar a câmera para mostrar bem o cenário. Testar o visual no celular.</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>Implementar os botões de navegação da história: Avançar (próximo trecho), Voltar (trecho anterior) e Reler (repetir o trecho atual). Os botões devem ficar na parte inferior da tela e ter feedback visual ao clicar.</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>Criar as artes 2D para a tela de narrativa: imagens de fundo para diferentes momentos da história, moldura para a área de texto, e elementos visuais de transição. Os assets devem ser leves para funcionar bem no celular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(O que fiz + Commit 2)</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="10" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(Tarefa 3)</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>Integrar todos os sistemas do jogo e garantir que o fluxo completo funciona: Menu → Seleção → Narrativa → Escolhas → Histórico. Testar em diferentes resoluções de celular e ajustar o layout se necessário.</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Montar o cenário blocado completo no Unity com os modelos criados. O cenário deve representar o ambiente da história e funcionar como sandbox para teste das funcionalidades. Garantir que o cenário está visível e funcional durante a narrativa.</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>Implementar transições visuais simples entre os trechos da história (ex: fade to black). As transições devem ser suaves e não atrapalhar a experiência. Adicionar efeitos sonoros nas transições.</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Testar todos os caminhos narrativos no jogo. Verificar ortografia e coerência dos textos. Confirmar que todas as escolhas levam aos trechos corretos. Testar a experiência de leitura na tela do celular e ajustar textos se necessário.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(O que fiz + Commit 3)</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr"/>
-      <c r="C27" s="10" t="inlineStr"/>
-      <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(Tarefa 4)</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Preparar e gerar a build final (APK) para a entrega. Testar a build em um celular real. Corrigir bugs críticos encontrados. Documentar a versão e o que está funcionando.</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Finalizar o GDR completo para entrega. Revisar todas as seções, adicionar screenshots do jogo no estado atual, incluir paleta de cores aplicada e link do moodboard. Exportar versão final.</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>Fazer testes finais de todas as mecânicas do jogo. Listar todos os bugs encontrados e corrigir os mais graves. Testar a performance no celular e garantir que o jogo roda bem.</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>Preparar o material de apresentação do projeto: resumo do conceito, público-alvo, decisões de design, estado atual e próximos passos. Incluir screenshots e fluxograma da narrativa. Preparar para validação com a instituição parceira.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>12/04 – 18/04
-(O que fiz + Commit 4)</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr"/>
-      <c r="D29" s="10" t="inlineStr"/>
-      <c r="E29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>SEMANA 3: 19/04 – 25/04 (Pós-entrega + Melhorias)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>André Henriques</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Antonio Araujo</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Arthur Doffémond</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>Laura Alairce</t>
+(Tarefa)</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Documentar no README as instruções de setup do projeto Unity e como rodar a build. Garantir que qualquer membro da equipe consiga abrir e trabalhar no projeto sem problemas.</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>Pesquisar e propor a paleta de cores oficial do projeto junto com a equipe. Apresentar opções com justificativa visual. Documentar no GDR. (Sugestão inicial: Amarelo Sol #F2C94C, Amarelo Escuro #D4A017, Marrom Terra #8B6914, Verde Musgo #556B2F, Cinza #808080).</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr"/>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>Criar esboços/wireframes da interface de narrativa: onde fica o texto da história, onde ficam os botões de escolha, como o jogador interage. Definir o layout básico dos botões do menu e de controle da narrativa (avançar, voltar). Compartilhar com a equipe para aprovação antes da implementação.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>19/04 – 25/04
-(Tarefa 1)</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Analisar o feedback recebido na entrega da build 1 e corrigir todos os bugs reportados. Melhorar a performance se necessário. Testar as correções no celular.</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Refinar os modelos 3D do cenário, adicionando mais detalhes e objetos de cenário (vegetação, objetos do dia a dia, etc). Manter o estilo low poly e garantir que continua leve para celular.</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Implementar sistema de salvar e carregar o progresso do jogador. O jogo deve salvar automaticamente o progresso a cada escolha e permitir que o jogador continue de onde parou.</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>Expandir a narrativa com mais detalhes, trechos de transição e diálogos adicionais. Revisar todos os textos com foco em linguagem clara e acessível para todas as idades.</t>
-        </is>
-      </c>
+          <t>05/04 – 11/04
+(O que fiz + Commit)</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>19/04 – 25/04
-(O que fiz + Commit 1)</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr"/>
-      <c r="C34" s="10" t="inlineStr"/>
-      <c r="D34" s="10" t="inlineStr"/>
-      <c r="E34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35"/>
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="33" t="inlineStr">
+        <is>
+          <t>SEMANA 2: 12/04 – 18/04 (FOCO TOTAL – Integração e Build)</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>SEMANA 4: 26/04 – 02/05 (Polimento + Próximo Ciclo)</t>
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Foco: Implementar narrativa + escolhas, integrar e gerar build. Interface segue wireframes da Semana 1. NÃO é prioridade: modelagem 3D detalhada, áudio, transições visuais, histórico de decisões.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>André Henriques</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="27" t="inlineStr">
         <is>
           <t>Antonio Araujo</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="27" t="inlineStr">
         <is>
           <t>Arthur Doffémond</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="27" t="inlineStr">
         <is>
           <t>Laura Alairce</t>
         </is>
@@ -1092,52 +1165,255 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>26/04 – 02/05
-(Tarefa 1)</t>
+          <t>12/04 – 18/04
+(Tarefa)</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Melhorar a acessibilidade do jogo: opção de aumentar/diminuir o tamanho da fonte, garantir bom contraste entre texto e fundo, e adicionar opção de narração automática. Testar com pessoas de diferentes idades.</t>
+          <t>Implementar o menu principal funcional com botões Iniciar e Sair. Usar elementos visuais simples (placeholders ok) seguindo a paleta definida na Semana 1. Fonte legível para todas as idades. Não precisa estar bonito — precisa funcionar.</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Criar assets 3D adicionais necessários para novos trechos da história. Criar animações simples para elementos do cenário (água, folhas, etc). Manter tudo leve e no estilo low poly.</t>
+          <t>Criar a blocagem básica de um cenário no Unity usando formas simples (cubos, planos, cilindros) para ter referência visual durante os testes. Aplicar cores sólidas da paleta. Sem detalhes, sem modelagem elaborada — apenas blocagem simples.</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Polir as transições e efeitos visuais do jogo. Melhorar o feedback visual dos botões. Adicionar efeitos visuais nos momentos importantes da narrativa.</t>
+          <t>Implementar o sistema básico de narrativa: exibir trechos de texto na tela e permitir avançar/voltar. A história pode ser armazenada como strings no código por enquanto — não precisa de JSON. Seguir o layout aprovado nos wireframes da Laura.</t>
         </is>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>Pesquisar e documentar possíveis histórias e personagens para as próximas versões do jogo. Criar uma estrutura narrativa base para o próximo personagem. Validar a abordagem com a instituição parceira.</t>
+          <t>Organizar a história do Benício em trechos prontos para o jogo: separar cada momento narrativo, listar as escolhas disponíveis e para onde cada uma leva. Verificar que não existem becos sem saída. Entregar para o Arthur em formato utilizável.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
+          <t>12/04 – 18/04
+(O que fiz + Commit)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>12/04 – 18/04
+(Tarefa)</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>Integrar todos os sistemas prontos, testar o fluxo completo (Menu → Narrativa → Escolhas) e gerar a build APK de teste. Testar em celular real se possível. Corrigir bugs críticos. Documentar o que funciona e o que falta.</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>Finalizar o GDR para entrega: revisar todas as seções, incluir links do moodboard, paleta oficial e direção de arte documentada. Garantir que o documento está completo.</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Implementar o sistema básico de escolhas: exibir botões de opção quando o texto apresenta uma escolha (seguindo layout da Laura). Cada escolha leva ao trecho correto. Testar com pelo menos 2 caminhos diferentes.</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>Testar todos os caminhos narrativos no jogo assim que o Arthur implementar. Verificar ortografia e coerência. Ajustar textos se necessário para ficarem bons na tela do celular (textos longos podem precisar ser divididos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>12/04 – 18/04
+(O que fiz + Commit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>SEMANA 3: 19/04 – 25/04 (Pós-entrega + Correções)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Foco: Analisar feedback da Build 1, corrigir problemas e começar a planejar melhorias para a Build 2 (entrega 17/05).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B45" s="35" t="inlineStr">
+        <is>
+          <t>André Henriques</t>
+        </is>
+      </c>
+      <c r="C45" s="35" t="inlineStr">
+        <is>
+          <t>Antonio Araujo</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="inlineStr">
+        <is>
+          <t>Arthur Doffémond</t>
+        </is>
+      </c>
+      <c r="E45" s="35" t="inlineStr">
+        <is>
+          <t>Laura Alairce</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>19/04 – 25/04
+(Tarefa)</t>
+        </is>
+      </c>
+      <c r="B46" s="30" t="inlineStr">
+        <is>
+          <t>Analisar o feedback recebido na entrega da Build 1. Listar problemas encontrados e priorizar correções. Corrigir bugs mais críticos. Testar correções.</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>Revisar e atualizar o GDR com o feedback recebido. Pesquisar novas referências se necessário. Começar a planejar quais elementos visuais precisaremos para a Build 2.</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>Corrigir bugs encontrados nas mecânicas de narrativa e escolhas. Melhorar a experiência de uso com base no feedback.</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>Revisar e ajustar textos narrativos com base no feedback. Escrever descrição dos cenários que precisaremos desenvolver futuramente para cada trecho da história (guia para artistas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>19/04 – 25/04
+(O que fiz + Commit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>SEMANA 4: 26/04 – 02/05 (Planejamento do Próximo Ciclo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Foco: Planejar a Build 2 com calma. Definir o que será adicionado e distribuir tarefas equilibradamente. Começar melhorias visuais e novas funcionalidades de forma gradual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B51" s="35" t="inlineStr">
+        <is>
+          <t>André Henriques</t>
+        </is>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>Antonio Araujo</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>Arthur Doffémond</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>Laura Alairce</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
+        <is>
           <t>26/04 – 02/05
-(O que fiz + Commit 1)</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr"/>
-      <c r="C39" s="10" t="inlineStr"/>
-      <c r="D39" s="10" t="inlineStr"/>
-      <c r="E39" s="10" t="inlineStr"/>
+(Tarefa)</t>
+        </is>
+      </c>
+      <c r="B52" s="30" t="inlineStr">
+        <is>
+          <t>Planejar melhorias e novas funcionalidades para a Build 2 (entrega 17/05). Organizar as tarefas e distribuir com a equipe, respeitando dependências e capacidade de cada um.</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>Começar planejamento visual mais detalhado dos cenários. Definir quais elementos visuais precisam ser criados para cada trecho da história. Organizar blocagem com cores da paleta oficial.</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
+        <is>
+          <t>Pesquisar e planejar melhorias técnicas para a Build 2 (ex: melhor organização do código da narrativa, possíveis melhorias de performance, estrutura para futuras funcionalidades).</t>
+        </is>
+      </c>
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>Pesquisar e documentar ideias para expandir a narrativa e interações futuras. Planejar interações secundárias (ex: interações com elementos do cenário como clicar em objetos). Definir prioridades para a Build 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>26/04 – 02/05
+(O que fiz + Commit)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A11:E11"/>
+  <mergeCells count="20">
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A49:E49"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A50:E50"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="B10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
